--- a/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tostada Aguacate" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Açaí Bowl" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Eggs Benedict" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tostada Aguacate" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Açaí Bowl" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eggs Benedict" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Tostada Aguacate'!$A$1:$I$26</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Açaí Bowl'!$A$1:$I$26</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Eggs Benedict'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tostada Aguacate'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tostada Aguacate'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Açaí Bowl'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Açaí Bowl'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Eggs Benedict'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Eggs Benedict'!$A$1:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,9 +27,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.000" numFmtId="165"/>
-    <numFmt formatCode="0.0%" numFmtId="166"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -171,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -351,112 +354,172 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="medium">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FFD700"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="51">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="3" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="3" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="5" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="5" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="4" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="12" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="13" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="4" fontId="0" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="0" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="6" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="7" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="5" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="5" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="14" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="15" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="13" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="4" fontId="16" numFmtId="9" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="16" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="14" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="14" fillId="6" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="17" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="14" fillId="0" fontId="13" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -816,15 +879,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -846,6 +910,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -887,10 +952,19 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -898,7 +972,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -907,23 +990,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -946,7 +1029,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1029,11 +1112,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1070,11 +1153,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>1.3888888888888888</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>2.083333333333333</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1111,11 +1194,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.18764044943820227</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.7880898876404495</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1152,11 +1235,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.04210526315789474</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.16842105263157897</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1198,11 +1281,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.010204081632653062</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.10204081632653061</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1239,11 +1322,11 @@
       </c>
       <c r="H10" s="20">
         <f>E10/(1-G10)</f>
-        <v/>
+        <v>0.010309278350515464</v>
       </c>
       <c r="I10" s="21">
         <f>H10*D10</f>
-        <v/>
+        <v>0.07731958762886598</v>
       </c>
       <c r="K10" s="22" t="n"/>
       <c r="L10" s="23" t="n"/>
@@ -1280,11 +1363,11 @@
       </c>
       <c r="H11" s="20">
         <f>E11/(1-G11)</f>
-        <v/>
+        <v>0.0020408163265306124</v>
       </c>
       <c r="I11" s="21">
         <f>H11*D11</f>
-        <v/>
+        <v>0.030612244897959186</v>
       </c>
       <c r="K11" s="22" t="n"/>
       <c r="L11" s="23" t="n"/>
@@ -1392,9 +1475,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="50" t="n"/>
       <c r="I18" s="36">
         <f>SUM(I5:I16)</f>
-        <v/>
+        <v>4.449816922458717</v>
       </c>
     </row>
     <row r="19">
@@ -1403,12 +1493,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
       <c r="H19" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I19" s="38">
         <f>I18*H19</f>
-        <v/>
+        <v>0.4449816922458717</v>
       </c>
     </row>
     <row r="20">
@@ -1417,9 +1513,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="50" t="n"/>
       <c r="I20" s="40">
         <f>I18+I19</f>
-        <v/>
+        <v>4.894798614704588</v>
       </c>
     </row>
     <row r="21"/>
@@ -1429,6 +1532,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
       <c r="H22" s="42" t="n">
         <v>0.28</v>
       </c>
@@ -1439,9 +1548,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="44">
         <f>I20/H22</f>
-        <v/>
+        <v>17.481423623944956</v>
       </c>
     </row>
     <row r="24">
@@ -1450,9 +1566,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="46">
         <f>I23*1.10</f>
-        <v/>
+        <v>19.229565986339452</v>
       </c>
     </row>
     <row r="25">
@@ -1461,9 +1584,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="50" t="n"/>
       <c r="I25" s="38">
         <f>I23-I20</f>
-        <v/>
+        <v>12.586625009240368</v>
       </c>
     </row>
     <row r="26">
@@ -1472,9 +1602,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="50" t="n"/>
       <c r="I26" s="47">
         <f>I25/I23</f>
-        <v/>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1619,6 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A26:H26"/>
@@ -1490,19 +1626,28 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1511,23 +1656,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1550,7 +1695,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -1633,11 +1778,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>0.10752688172043012</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>2.365591397849463</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -1674,11 +1819,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.16</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.24</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -1715,11 +1860,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.08247422680412371</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>0.20618556701030927</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -1756,11 +1901,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.04081632653061225</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.326530612244898</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -1802,11 +1947,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.031578947368421054</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.37894736842105264</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -1843,11 +1988,11 @@
       </c>
       <c r="H10" s="20">
         <f>E10/(1-G10)</f>
-        <v/>
+        <v>0.010204081632653062</v>
       </c>
       <c r="I10" s="21">
         <f>H10*D10</f>
-        <v/>
+        <v>0.07142857142857144</v>
       </c>
       <c r="K10" s="22" t="n"/>
       <c r="L10" s="23" t="n"/>
@@ -1884,11 +2029,11 @@
       </c>
       <c r="H11" s="20">
         <f>E11/(1-G11)</f>
-        <v/>
+        <v>0.015463917525773196</v>
       </c>
       <c r="I11" s="21">
         <f>H11*D11</f>
-        <v/>
+        <v>0.15463917525773196</v>
       </c>
       <c r="K11" s="22" t="n"/>
       <c r="L11" s="23" t="n"/>
@@ -1996,9 +2141,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="50" t="n"/>
       <c r="I18" s="36">
         <f>SUM(I5:I16)</f>
-        <v/>
+        <v>3.7433226922120264</v>
       </c>
     </row>
     <row r="19">
@@ -2007,12 +2159,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="50" t="n"/>
       <c r="H19" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I19" s="38">
         <f>I18*H19</f>
-        <v/>
+        <v>0.37433226922120266</v>
       </c>
     </row>
     <row r="20">
@@ -2021,9 +2179,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="49" t="n"/>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="50" t="n"/>
       <c r="I20" s="40">
         <f>I18+I19</f>
-        <v/>
+        <v>4.117654961433229</v>
       </c>
     </row>
     <row r="21"/>
@@ -2033,6 +2198,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="50" t="n"/>
       <c r="H22" s="42" t="n">
         <v>0.28</v>
       </c>
@@ -2043,9 +2214,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="44">
         <f>I20/H22</f>
-        <v/>
+        <v>14.705910576547245</v>
       </c>
     </row>
     <row r="24">
@@ -2054,9 +2232,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="46">
         <f>I23*1.10</f>
-        <v/>
+        <v>16.17650163420197</v>
       </c>
     </row>
     <row r="25">
@@ -2065,9 +2250,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="50" t="n"/>
       <c r="I25" s="38">
         <f>I23-I20</f>
-        <v/>
+        <v>10.588255615114015</v>
       </c>
     </row>
     <row r="26">
@@ -2076,9 +2268,16 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="50" t="n"/>
       <c r="I26" s="47">
         <f>I25/I23</f>
-        <v/>
+        <v>0.7199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2285,6 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A26:H26"/>
@@ -2094,19 +2292,28 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2115,23 +2322,23 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="25"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="10"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="3"/>
-    <col customWidth="1" max="11" min="11" width="20"/>
-    <col customWidth="1" max="12" min="12" width="20"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2154,7 +2361,7 @@
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="11" t="n"/>
+      <c r="L3" s="48" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -2237,11 +2444,11 @@
       </c>
       <c r="H5" s="20">
         <f>E5/(1-G5)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="I5" s="21">
         <f>H5*D5</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="K5" s="22" t="n"/>
       <c r="L5" s="23" t="n"/>
@@ -2278,11 +2485,11 @@
       </c>
       <c r="H6" s="20">
         <f>E6/(1-G6)</f>
-        <v/>
+        <v>0.18764044943820227</v>
       </c>
       <c r="I6" s="21">
         <f>H6*D6</f>
-        <v/>
+        <v>0.7880898876404495</v>
       </c>
       <c r="K6" s="22" t="n"/>
       <c r="L6" s="23" t="n"/>
@@ -2319,11 +2526,11 @@
       </c>
       <c r="H7" s="20">
         <f>E7/(1-G7)</f>
-        <v/>
+        <v>0.06315789473684211</v>
       </c>
       <c r="I7" s="21">
         <f>H7*D7</f>
-        <v/>
+        <v>2.210526315789474</v>
       </c>
       <c r="K7" s="22" t="n"/>
       <c r="L7" s="23" t="n"/>
@@ -2360,11 +2567,11 @@
       </c>
       <c r="H8" s="20">
         <f>E8/(1-G8)</f>
-        <v/>
+        <v>0.051546391752577324</v>
       </c>
       <c r="I8" s="21">
         <f>H8*D8</f>
-        <v/>
+        <v>0.4639175257731959</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -2406,11 +2613,11 @@
       </c>
       <c r="H9" s="20">
         <f>E9/(1-G9)</f>
-        <v/>
+        <v>0.01388888888888889</v>
       </c>
       <c r="I9" s="21">
         <f>H9*D9</f>
-        <v/>
+        <v>0.034722222222222224</v>
       </c>
       <c r="K9" s="26" t="n"/>
       <c r="L9" s="27" t="n"/>
@@ -2447,11 +2654,11 @@
       </c>
       <c r="H10" s="20">
         <f>E10/(1-G10)</f>
-        <v/>
+        <v>0.3125</v>
       </c>
       <c r="I10" s="21">
         <f>H10*D10</f>
-        <v/>
+        <v>0.46875</v>
       </c>
       <c r="K10" s="22" t="n"/>
       <c r="L10" s="23" t="n"/>
@@ -2561,9 +2768,16 @@
           <t>COSTE TOTAL INGREDIENTES</t>
         </is>
       </c>
+      <c r="B17" s="49" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="49" t="n"/>
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
       <c r="I17" s="36">
         <f>SUM(I5:I15)</f>
-        <v/>
+        <v>4.766005951425342</v>
       </c>
     </row>
     <row r="18">
@@ -2572,12 +2786,18 @@
           <t>Coste elaboración (%)</t>
         </is>
       </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="49" t="n"/>
+      <c r="G18" s="50" t="n"/>
       <c r="H18" s="19" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" s="38">
         <f>I17*H18</f>
-        <v/>
+        <v>0.4766005951425342</v>
       </c>
     </row>
     <row r="19">
@@ -2586,9 +2806,16 @@
           <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
+      <c r="B19" s="49" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="49" t="n"/>
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="50" t="n"/>
       <c r="I19" s="40">
         <f>I17+I18</f>
-        <v/>
+        <v>5.242606546567876</v>
       </c>
     </row>
     <row r="20"/>
@@ -2598,6 +2825,12 @@
           <t>Food Cost objetivo (%)</t>
         </is>
       </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="50" t="n"/>
       <c r="H21" s="42" t="n">
         <v>0.28</v>
       </c>
@@ -2608,9 +2841,16 @@
           <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
       <c r="I22" s="44">
         <f>I19/H21</f>
-        <v/>
+        <v>18.723594809170983</v>
       </c>
     </row>
     <row r="23">
@@ -2619,9 +2859,16 @@
           <t>PVP CON IVA (10% hostelería)</t>
         </is>
       </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="50" t="n"/>
       <c r="I23" s="46">
         <f>I22*1.10</f>
-        <v/>
+        <v>20.595954290088084</v>
       </c>
     </row>
     <row r="24">
@@ -2630,9 +2877,16 @@
           <t>Margen bruto (€)</t>
         </is>
       </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
       <c r="I24" s="38">
         <f>I22-I19</f>
-        <v/>
+        <v>13.480988262603107</v>
       </c>
     </row>
     <row r="25">
@@ -2641,16 +2895,22 @@
           <t>Margen bruto (%)</t>
         </is>
       </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="50" t="n"/>
       <c r="I25" s="47">
         <f>I24/I22</f>
-        <v/>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A18:G18"/>
@@ -2660,17 +2920,26 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A23:H23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Selecciona una categoría válida" errorTitle="Categoría inválida" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
       <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" type="list">
+    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
+++ b/astro-site/public/dl/kit-escandallos/07-cafeteria-brunch.xlsx
@@ -11,14 +11,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tostada Aguacate" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Açaí Bowl" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eggs Benedict" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carrot Cake" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conversiones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mermas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tostada Aguacate'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tostada Aguacate'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Tostada Aguacate'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Açaí Bowl'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Açaí Bowl'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Açaí Bowl'!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Eggs Benedict'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Eggs Benedict'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Eggs Benedict'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Carrot Cake'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Carrot Cake'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Conversiones'!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Mermas'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,12 +33,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.###"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +143,20 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -171,6 +191,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD700"/>
         <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -415,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -515,10 +550,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="9" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="9" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -881,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -919,52 +1027,330 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>▸ 3 recetas típicas de brunch/cafetería</t>
+          <t>▸ 4 recetas típicas de brunch y cafetería: tostada de aguacate, açaí bowl, eggs benedict y carrot cake.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>▸ Food cost objetivo en cafetería: 25-30%</t>
+          <t>▸ La carrot cake se escandalla por tanda: 12 raciones en «Nº de raciones» y el coste por porción sale solo.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>▸ Ideal para calcular precios de carta de brunch</t>
+          <t>▸ Food cost objetivo de referencia en cafetería: 25-30 %.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>▸ Las celdas VERDES son las editables; el resto son fórmulas.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Columnas de la hoja de escandallo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>▸ Ingrediente: el producto tal como lo compras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>▸ Categoría: familia del ingrediente (desplegable). Es la que precarga la merma en las filas vacías.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>▸ Ud. Compra: la unidad en la que COMPRAS (kg, L, docena, manojo…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>▸ Precio/Ud (€): lo que pagas por esa unidad de compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>▸ Cantidad: la que usas en el plato, EN LA UNIDAD DE USO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>▸ Ud. Uso: la unidad en la que mides al cocinar (g, ml, cl, ud…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>▸ Factor: conversión automática Ud. Compra → Ud. Uso, de la hoja «Conversiones». Si la pareja NO está en la tabla, el Factor se pone en rojo con un «?» y el Coste dice «revisa unidades»: añade la equivalencia en «Conversiones» antes de fiarte del número. Nunca da un coste plausible y falso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>▸ Merma (%): desperdicio. En las filas de ejemplo está escrita a mano; en las vacías la trae la hoja «Mermas» en cuanto eliges categoría, y puedes escribir encima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>▸ Ojo con la merma cuando mides en PIEZAS: la del 11 % de los huevos es la CÁSCARA, y sólo tiene sentido sobre el peso. Si compras y mides en unidades, déjala en 0 %: seis huevos son seis huevos, no 6,74. La misma regla vale para cualquier ingrediente que cuentes por unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>▸ Cant. Bruta: lo que hay que comprar contando la merma (automático).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>▸ Coste (€): Cant. Bruta × Precio/Ud ÷ Factor (automático).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Bloque de resultado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>▸ Coste elaboración (%): recargo sobre la materia prima para cubrir energía, envasado y pérdidas de preparación que no se escandallan línea a línea. Viene al 10 %; ponlo a 0 % si prefieres imputar esos costes aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>▸ COSTE TOTAL DEL PLATO: materia prima + coste de elaboración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>▸ Nº de raciones: cuántas raciones salen de lo escandallado. Déjalo en 1 si es un plato individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>▸ COSTE POR RACIÓN: coste total ÷ raciones. Es la base del PVP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>▸ Food Cost objetivo (%): el que quieres conseguir. PVP sin IVA = coste por ración ÷ food cost objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>▸ Tipo de IVA (%): editable. 10 % en hostelería en España; cámbialo si te aplica otro tipo (IGIC en Canarias, o el IVA/ITBIS/IVU de tu país en Latinoamérica).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>▸ PVP actual en carta (sin IVA): lo que cobras HOY. Déjalo vacío si todavía no lo tienes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>▸ FOOD COST REAL (%): coste por ración ÷ PVP actual. Se pone en rojo en cuanto supera tu objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Hojas auxiliares</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>▸ «Conversiones»: equivalencias Ud. Compra → Ud. Uso. Va SIN protección: añade las parejas que te falten y corrige el tamaño de los formatos (la botella viene a 70 cl y la lata a 33 cl; si tu vino es de 75 cl, cambia el 70 por 75 en «botella→cl»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>▸ «Mermas»: merma mínima, típica y máxima por categoría. La típica es la que se precarga en las filas vacías.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>▸ Las hojas están protegidas SIN contraseña para que no borres una fórmula sin querer: sólo se escriben las celdas verdes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>▸ Para tocar cualquier otra cosa —insertar filas, pegar la foto del plato, cambiar una fórmula—: Revisar → Desproteger hoja. No pide contraseña.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>▸ Si te quedas sin filas: desprotege la hoja e inserta filas DENTRO del bloque de ingredientes (clic derecho sobre una fila del bloque → Insertar), nunca debajo de la última. Así el «COSTE TOTAL INGREDIENTES» las recoge solo; lo que escribas por debajo del bloque NO suma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>▸ La foto del plato NO se puede arrastrar con la hoja protegida: primero Revisar → Desproteger hoja, y después Insertar → Imagen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de mermas estándar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>▸ Carne roja 20 % | Aves 25 % | Pescado 35 % | Marisco 45 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>▸ Verdura hoja 25 % | Verdura raíz 12 % | Verdura fruto 10 % | Fruta 15 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>▸ Lácteos 3 % | Secos/granos 2 % | Congelados 7 % | Pan/bollería 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>▸ Huevos 11 % | Aceites/grasas 3 % | Especias/hierbas 20 % | Chocolate/cacao 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>▸ Bebidas/licores 2 % | Setas/hongos 20 % | Conservas/encurtidos 8 % | Salsas/condimentos 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>▸ Pasta/arroz 2 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>▸ Son las 21 categorías del desplegable. La tabla completa, con mínimo y máximo, está en la hoja «Mermas».</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>— Kit de Escandallos Pro · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · Todos los derechos reservados</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
+    <row r="63"/>
+    <row r="64">
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-escandallos · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -992,7 +1378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1001,12 +1387,13 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,22 +1403,22 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Introduce tus ingredientes y cantidades. Las celdas verdes son editables.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="K3" s="10" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="48" t="n"/>
-    </row>
-    <row r="4">
+      <c r="M3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Ingrediente</t>
@@ -1064,488 +1451,600 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
           <t>Merma (%)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Cant. Bruta</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Coste (€)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="14" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Pan de masa madre</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>Pan de masa madre (rebanada gruesa)</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Pan/bollería</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="54" t="n">
         <v>0.6</v>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="E5" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="56">
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="20">
-        <f>E5/(1-G5)</f>
-        <v>2.0</v>
-      </c>
-      <c r="I5" s="21">
-        <f>H5*D5</f>
-        <v>1.2</v>
-      </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="23" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Aguacate Hass</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="I5" s="20">
+        <f>IFERROR(IF(E5="","",E5/(1-H5)),"revisa merma")</f>
+        <v>1.0</v>
+      </c>
+      <c r="J5" s="21">
+        <f>IF(G5="?","revisa unidades",IFERROR(I5*D5/G5,""))</f>
+        <v>0.6</v>
+      </c>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>Aguacate Hass (½ pieza)</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>Fruta</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="G6" s="56">
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I6" s="20">
+        <f>IFERROR(IF(E6="","",E6/(1-H6)),"revisa merma")</f>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="J6" s="21">
+        <f>IF(G6="?","revisa unidades",IFERROR(I6*D6/G6,""))</f>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>Huevo campero</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>docena</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E7" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H6" s="20">
-        <f>E6/(1-G6)</f>
-        <v>1.3888888888888888</v>
-      </c>
-      <c r="I6" s="21">
-        <f>H6*D6</f>
-        <v>2.083333333333333</v>
-      </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="23" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Huevo campero</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Huevos</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>docena</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H7" s="20">
-        <f>E7/(1-G7)</f>
-        <v>0.18764044943820227</v>
-      </c>
-      <c r="I7" s="21">
-        <f>H7*D7</f>
-        <v>0.7880898876404495</v>
-      </c>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="23" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="G7" s="56">
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>12.0</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="20">
+        <f>IFERROR(IF(E7="","",E7/(1-H7)),"revisa merma")</f>
+        <v>1.0</v>
+      </c>
+      <c r="J7" s="21">
+        <f>IF(G7="?","revisa unidades",IFERROR(I7*D7/G7,""))</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Tomate cherry</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Verdura hoja</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Verdura fruto</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="55" t="n">
         <v>0.04</v>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="56">
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="20">
-        <f>E8/(1-G8)</f>
+      <c r="I8" s="20">
+        <f>IFERROR(IF(E8="","",E8/(1-H8)),"revisa merma")</f>
         <v>0.04210526315789474</v>
       </c>
-      <c r="I8" s="21">
-        <f>H8*D8</f>
+      <c r="J8" s="21">
+        <f>IF(G8="?","revisa unidades",IFERROR(I8*D8/G8,""))</f>
         <v>0.16842105263157897</v>
       </c>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>Arrastra aquí la foto
-del plato terminado</t>
-        </is>
-      </c>
-      <c r="L8" s="25" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Foto del plato terminado:
+Revisar → Desproteger hoja,
+luego Insertar → Imagen</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Semillas mix</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="55" t="n">
         <v>0.01</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="56">
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="H9" s="20">
-        <f>E9/(1-G9)</f>
+      <c r="I9" s="20">
+        <f>IFERROR(IF(E9="","",E9/(1-H9)),"revisa merma")</f>
         <v>0.010204081632653062</v>
       </c>
-      <c r="I9" s="21">
-        <f>H9*D9</f>
+      <c r="J9" s="21">
+        <f>IF(G9="?","revisa unidades",IFERROR(I9*D9/G9,""))</f>
         <v>0.10204081632653061</v>
       </c>
-      <c r="K9" s="26" t="n"/>
-      <c r="L9" s="27" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>AOVE</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>Aceites/grasas</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="54" t="n">
         <v>7.5</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="55" t="n">
         <v>0.01</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="56">
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="H10" s="20">
-        <f>E10/(1-G10)</f>
+      <c r="I10" s="20">
+        <f>IFERROR(IF(E10="","",E10/(1-H10)),"revisa merma")</f>
         <v>0.010309278350515464</v>
       </c>
-      <c r="I10" s="21">
-        <f>H10*D10</f>
+      <c r="J10" s="21">
+        <f>IF(G10="?","revisa unidades",IFERROR(I10*D10/G10,""))</f>
         <v>0.07731958762886598</v>
       </c>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="23" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Sal en escamas</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="54" t="n">
         <v>15</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="55" t="n">
         <v>0.002</v>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="56">
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="H11" s="20">
-        <f>E11/(1-G11)</f>
+      <c r="I11" s="20">
+        <f>IFERROR(IF(E11="","",E11/(1-H11)),"revisa merma")</f>
         <v>0.0020408163265306124</v>
       </c>
-      <c r="I11" s="21">
-        <f>H11*D11</f>
+      <c r="J11" s="21">
+        <f>IF(G11="?","revisa unidades",IFERROR(I11*D11/G11,""))</f>
         <v>0.030612244897959186</v>
       </c>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="23" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="30">
-        <f>IF(E12="","",E12/(1-G12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>IF(H12="","",H12*D12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="23" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="30">
-        <f>IF(E13="","",E13/(1-G13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="31">
-        <f>IF(H13="","",H13*D13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="23" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="30">
-        <f>IF(E14="","",E14/(1-G14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="31">
-        <f>IF(H14="","",H14*D14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="58" t="n"/>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="58" t="n"/>
+      <c r="G12" s="56">
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>IFERROR(VLOOKUP(B12,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="30">
+        <f>IFERROR(IF(E12="","",E12/(1-H12)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J12" s="31">
+        <f>IF(G12="?","revisa unidades",IFERROR(I12*D12/G12,""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="C13" s="58" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="56">
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="59">
+        <f>IFERROR(VLOOKUP(B13,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="30">
+        <f>IFERROR(IF(E13="","",E13/(1-H13)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>IF(G13="?","revisa unidades",IFERROR(I13*D13/G13,""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="56">
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="59">
+        <f>IFERROR(VLOOKUP(B14,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>IFERROR(IF(E14="","",E14/(1-H14)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J14" s="31">
+        <f>IF(G14="?","revisa unidades",IFERROR(I14*D14/G14,""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="30">
-        <f>IF(E15="","",E15/(1-G15))</f>
-        <v/>
-      </c>
-      <c r="I15" s="31">
-        <f>IF(H15="","",H15*D15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="34" t="inlineStr">
-        <is>
-          <t>Insertar → Imagen → Desde archivo</t>
-        </is>
-      </c>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="56">
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>IFERROR(VLOOKUP(B15,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="30">
+        <f>IFERROR(IF(E15="","",E15/(1-H15)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J15" s="31">
+        <f>IF(G15="?","revisa unidades",IFERROR(I15*D15/G15,""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="34" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="30">
-        <f>IF(E16="","",E16/(1-G16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="31">
-        <f>IF(H16="","",H16*D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="56">
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="59">
+        <f>IFERROR(VLOOKUP(B16,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="30">
+        <f>IFERROR(IF(E16="","",E16/(1-H16)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J16" s="31">
+        <f>IF(G16="?","revisa unidades",IFERROR(I16*D16/G16,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="56">
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="59">
+        <f>IFERROR(VLOOKUP(B17,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>IFERROR(IF(E17="","",E17/(1-H17)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J17" s="31">
+        <f>IF(G17="?","revisa unidades",IFERROR(I17*D17/G17,""))</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="56">
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="59">
+        <f>IFERROR(VLOOKUP(B18,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="30">
+        <f>IFERROR(IF(E18="","",E18/(1-H18)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J18" s="31">
+        <f>IF(G18="?","revisa unidades",IFERROR(I18*D18/G18,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="n"/>
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="56">
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>IFERROR(VLOOKUP(B19,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="30">
+        <f>IFERROR(IF(E19="","",E19/(1-H19)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>IF(G19="?","revisa unidades",IFERROR(I19*D19/G19,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="n"/>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="56">
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>IFERROR(VLOOKUP(B20,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="30">
+        <f>IFERROR(IF(E20="","",E20/(1-H20)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J20" s="31">
+        <f>IF(G20="?","revisa unidades",IFERROR(I20*D20/G20,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="n"/>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="56">
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="59">
+        <f>IFERROR(VLOOKUP(B21,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="30">
+        <f>IFERROR(IF(E21="","",E21/(1-H21)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J21" s="31">
+        <f>IF(G21="?","revisa unidades",IFERROR(I21*D21/G21,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>COSTE TOTAL INGREDIENTES</t>
-        </is>
-      </c>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="49" t="n"/>
-      <c r="G18" s="49" t="n"/>
-      <c r="H18" s="50" t="n"/>
-      <c r="I18" s="36">
-        <f>SUM(I5:I16)</f>
-        <v>4.449816922458717</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>Coste elaboración (%)</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="49" t="n"/>
-      <c r="G19" s="50" t="n"/>
-      <c r="H19" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" s="38">
-        <f>I18*H19</f>
-        <v>0.4449816922458717</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>COSTE TOTAL DEL PLATO</t>
-        </is>
-      </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="50" t="n"/>
-      <c r="I20" s="40">
-        <f>I18+I19</f>
-        <v>4.894798614704588</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="41" t="inlineStr">
-        <is>
-          <t>Food Cost objetivo (%)</t>
-        </is>
-      </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="42" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
       <c r="B23" s="49" t="n"/>
@@ -1554,16 +2053,17 @@
       <c r="E23" s="49" t="n"/>
       <c r="F23" s="49" t="n"/>
       <c r="G23" s="49" t="n"/>
-      <c r="H23" s="50" t="n"/>
-      <c r="I23" s="44">
-        <f>I20/H22</f>
-        <v>17.481423623944956</v>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="36">
+        <f>SUM(J5:J21)</f>
+        <v>2.1617270348182687</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>PVP CON IVA (10% hostelería)</t>
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Coste elaboración (%)</t>
         </is>
       </c>
       <c r="B24" s="49" t="n"/>
@@ -1573,15 +2073,18 @@
       <c r="F24" s="49" t="n"/>
       <c r="G24" s="49" t="n"/>
       <c r="H24" s="50" t="n"/>
-      <c r="I24" s="46">
-        <f>I23*1.10</f>
-        <v>19.229565986339452</v>
+      <c r="I24" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="38">
+        <f>J23*I24</f>
+        <v>0.21617270348182688</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>Margen bruto (€)</t>
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
       <c r="B25" s="49" t="n"/>
@@ -1590,16 +2093,17 @@
       <c r="E25" s="49" t="n"/>
       <c r="F25" s="49" t="n"/>
       <c r="G25" s="49" t="n"/>
-      <c r="H25" s="50" t="n"/>
-      <c r="I25" s="38">
-        <f>I23-I20</f>
-        <v>12.586625009240368</v>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="40">
+        <f>J23+J24</f>
+        <v>2.3778997383000955</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>Margen bruto (%)</t>
+          <t>Nº de raciones</t>
         </is>
       </c>
       <c r="B26" s="49" t="n"/>
@@ -1609,32 +2113,215 @@
       <c r="F26" s="49" t="n"/>
       <c r="G26" s="49" t="n"/>
       <c r="H26" s="50" t="n"/>
-      <c r="I26" s="47">
-        <f>I25/I23</f>
+      <c r="I26" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>COSTE POR RACIÓN</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="40">
+        <f>IFERROR(J25/I26,"")</f>
+        <v>2.3778997383000955</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Food Cost objetivo (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="62" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>PVP SUGERIDO (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="50" t="n"/>
+      <c r="J30" s="44">
+        <f>IFERROR(J27/I29,"")</f>
+        <v>8.492499065357483</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Tipo de IVA (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>PVP CON IVA</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="40">
+        <f>IFERROR(J30*(1+I31),"")</f>
+        <v>9.341748971893233</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Margen bruto (€)</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="44">
+        <f>IFERROR(J30-J27,"")</f>
+        <v>6.1145993270573875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>Margen bruto (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="47">
+        <f>IFERROR((J30-J27)/J30,"")</f>
         <v>0.72</v>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>PVP actual en carta (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="63" t="n"/>
+      <c r="J36" s="38" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>FOOD COST REAL (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="49" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="64">
+        <f>IFERROR(J27/I36,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A20:H20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G5:G21">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"?"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISNUMBER($J$37),$J$37&gt;$I$29)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
-      <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
+    <dataValidation sqref="B5:B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista (hoja «Mermas»)." type="list">
+      <formula1>Mermas!$A$5:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C21 F5:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una unidad de la lista." type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1658,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1667,12 +2354,13 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1682,22 +2370,22 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Introduce tus ingredientes y cantidades. Las celdas verdes son editables.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="K3" s="10" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="48" t="n"/>
-    </row>
-    <row r="4">
+      <c r="M3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Ingrediente</t>
@@ -1730,488 +2418,600 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
           <t>Merma (%)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Cant. Bruta</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Coste (€)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="14" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Açaí congelado</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Congelados</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="55" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="56">
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="57" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H5" s="20">
-        <f>E5/(1-G5)</f>
+      <c r="I5" s="20">
+        <f>IFERROR(IF(E5="","",E5/(1-H5)),"revisa merma")</f>
         <v>0.10752688172043012</v>
       </c>
-      <c r="I5" s="21">
-        <f>H5*D5</f>
+      <c r="J5" s="21">
+        <f>IF(G5="?","revisa unidades",IFERROR(I5*D5/G5,""))</f>
         <v>2.365591397849463</v>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="23" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Plátano</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>Fruta</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="55" t="n">
         <v>0.12</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="56">
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="57" t="n">
         <v>0.25</v>
       </c>
-      <c r="H6" s="20">
-        <f>E6/(1-G6)</f>
+      <c r="I6" s="20">
+        <f>IFERROR(IF(E6="","",E6/(1-H6)),"revisa merma")</f>
         <v>0.16</v>
       </c>
-      <c r="I6" s="21">
-        <f>H6*D6</f>
+      <c r="J6" s="21">
+        <f>IF(G6="?","revisa unidades",IFERROR(I6*D6/G6,""))</f>
         <v>0.24</v>
       </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="23" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Leche de avena</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>Bebidas/licores</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="55" t="n">
         <v>0.08</v>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="56">
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="H7" s="20">
-        <f>E7/(1-G7)</f>
+      <c r="I7" s="20">
+        <f>IFERROR(IF(E7="","",E7/(1-H7)),"revisa merma")</f>
         <v>0.08247422680412371</v>
       </c>
-      <c r="I7" s="21">
-        <f>H7*D7</f>
+      <c r="J7" s="21">
+        <f>IF(G7="?","revisa unidades",IFERROR(I7*D7/G7,""))</f>
         <v>0.20618556701030927</v>
       </c>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="23" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Granola artesanal</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="55" t="n">
         <v>0.04</v>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="56">
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="H8" s="20">
-        <f>E8/(1-G8)</f>
+      <c r="I8" s="20">
+        <f>IFERROR(IF(E8="","",E8/(1-H8)),"revisa merma")</f>
         <v>0.04081632653061225</v>
       </c>
-      <c r="I8" s="21">
-        <f>H8*D8</f>
+      <c r="J8" s="21">
+        <f>IF(G8="?","revisa unidades",IFERROR(I8*D8/G8,""))</f>
         <v>0.326530612244898</v>
       </c>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>Arrastra aquí la foto
-del plato terminado</t>
-        </is>
-      </c>
-      <c r="L8" s="25" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Foto del plato terminado:
+Revisar → Desproteger hoja,
+luego Insertar → Imagen</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Arándanos</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Fruta</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="55" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="56">
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="20">
-        <f>E9/(1-G9)</f>
+      <c r="I9" s="20">
+        <f>IFERROR(IF(E9="","",E9/(1-H9)),"revisa merma")</f>
         <v>0.031578947368421054</v>
       </c>
-      <c r="I9" s="21">
-        <f>H9*D9</f>
+      <c r="J9" s="21">
+        <f>IF(G9="?","revisa unidades",IFERROR(I9*D9/G9,""))</f>
         <v>0.37894736842105264</v>
       </c>
-      <c r="K9" s="26" t="n"/>
-      <c r="L9" s="27" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>Coco rallado</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="54" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="55" t="n">
         <v>0.01</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="56">
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="57" t="n">
         <v>0.02</v>
       </c>
-      <c r="H10" s="20">
-        <f>E10/(1-G10)</f>
+      <c r="I10" s="20">
+        <f>IFERROR(IF(E10="","",E10/(1-H10)),"revisa merma")</f>
         <v>0.010204081632653062</v>
       </c>
-      <c r="I10" s="21">
-        <f>H10*D10</f>
+      <c r="J10" s="21">
+        <f>IF(G10="?","revisa unidades",IFERROR(I10*D10/G10,""))</f>
         <v>0.07142857142857144</v>
       </c>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="23" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Miel</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>Secos/granos</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="55" t="n">
         <v>0.015</v>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="56">
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="H11" s="20">
-        <f>E11/(1-G11)</f>
+      <c r="I11" s="20">
+        <f>IFERROR(IF(E11="","",E11/(1-H11)),"revisa merma")</f>
         <v>0.015463917525773196</v>
       </c>
-      <c r="I11" s="21">
-        <f>H11*D11</f>
+      <c r="J11" s="21">
+        <f>IF(G11="?","revisa unidades",IFERROR(I11*D11/G11,""))</f>
         <v>0.15463917525773196</v>
       </c>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="23" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="30">
-        <f>IF(E12="","",E12/(1-G12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>IF(H12="","",H12*D12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="23" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="30">
-        <f>IF(E13="","",E13/(1-G13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="31">
-        <f>IF(H13="","",H13*D13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="23" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="30">
-        <f>IF(E14="","",E14/(1-G14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="31">
-        <f>IF(H14="","",H14*D14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="58" t="n"/>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="58" t="n"/>
+      <c r="G12" s="56">
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>IFERROR(VLOOKUP(B12,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="30">
+        <f>IFERROR(IF(E12="","",E12/(1-H12)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J12" s="31">
+        <f>IF(G12="?","revisa unidades",IFERROR(I12*D12/G12,""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="C13" s="58" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="56">
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="59">
+        <f>IFERROR(VLOOKUP(B13,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="30">
+        <f>IFERROR(IF(E13="","",E13/(1-H13)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>IF(G13="?","revisa unidades",IFERROR(I13*D13/G13,""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="56">
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="59">
+        <f>IFERROR(VLOOKUP(B14,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>IFERROR(IF(E14="","",E14/(1-H14)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J14" s="31">
+        <f>IF(G14="?","revisa unidades",IFERROR(I14*D14/G14,""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="30">
-        <f>IF(E15="","",E15/(1-G15))</f>
-        <v/>
-      </c>
-      <c r="I15" s="31">
-        <f>IF(H15="","",H15*D15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="34" t="inlineStr">
-        <is>
-          <t>Insertar → Imagen → Desde archivo</t>
-        </is>
-      </c>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="56">
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>IFERROR(VLOOKUP(B15,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="30">
+        <f>IFERROR(IF(E15="","",E15/(1-H15)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J15" s="31">
+        <f>IF(G15="?","revisa unidades",IFERROR(I15*D15/G15,""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="34" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="28" t="n"/>
-      <c r="C16" s="28" t="n"/>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="28" t="n"/>
-      <c r="F16" s="28" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="30">
-        <f>IF(E16="","",E16/(1-G16))</f>
-        <v/>
-      </c>
-      <c r="I16" s="31">
-        <f>IF(H16="","",H16*D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="56">
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="59">
+        <f>IFERROR(VLOOKUP(B16,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="30">
+        <f>IFERROR(IF(E16="","",E16/(1-H16)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J16" s="31">
+        <f>IF(G16="?","revisa unidades",IFERROR(I16*D16/G16,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="56">
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="59">
+        <f>IFERROR(VLOOKUP(B17,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>IFERROR(IF(E17="","",E17/(1-H17)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J17" s="31">
+        <f>IF(G17="?","revisa unidades",IFERROR(I17*D17/G17,""))</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="56">
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="59">
+        <f>IFERROR(VLOOKUP(B18,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="30">
+        <f>IFERROR(IF(E18="","",E18/(1-H18)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J18" s="31">
+        <f>IF(G18="?","revisa unidades",IFERROR(I18*D18/G18,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="n"/>
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="56">
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>IFERROR(VLOOKUP(B19,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="30">
+        <f>IFERROR(IF(E19="","",E19/(1-H19)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>IF(G19="?","revisa unidades",IFERROR(I19*D19/G19,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="n"/>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="56">
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>IFERROR(VLOOKUP(B20,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="30">
+        <f>IFERROR(IF(E20="","",E20/(1-H20)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J20" s="31">
+        <f>IF(G20="?","revisa unidades",IFERROR(I20*D20/G20,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="n"/>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="56">
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="59">
+        <f>IFERROR(VLOOKUP(B21,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="30">
+        <f>IFERROR(IF(E21="","",E21/(1-H21)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J21" s="31">
+        <f>IF(G21="?","revisa unidades",IFERROR(I21*D21/G21,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>COSTE TOTAL INGREDIENTES</t>
-        </is>
-      </c>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="49" t="n"/>
-      <c r="G18" s="49" t="n"/>
-      <c r="H18" s="50" t="n"/>
-      <c r="I18" s="36">
-        <f>SUM(I5:I16)</f>
-        <v>3.7433226922120264</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>Coste elaboración (%)</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="49" t="n"/>
-      <c r="G19" s="50" t="n"/>
-      <c r="H19" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" s="38">
-        <f>I18*H19</f>
-        <v>0.37433226922120266</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>COSTE TOTAL DEL PLATO</t>
-        </is>
-      </c>
-      <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="49" t="n"/>
-      <c r="G20" s="49" t="n"/>
-      <c r="H20" s="50" t="n"/>
-      <c r="I20" s="40">
-        <f>I18+I19</f>
-        <v>4.117654961433229</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="41" t="inlineStr">
-        <is>
-          <t>Food Cost objetivo (%)</t>
-        </is>
-      </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="49" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="49" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="42" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
       <c r="B23" s="49" t="n"/>
@@ -2220,16 +3020,17 @@
       <c r="E23" s="49" t="n"/>
       <c r="F23" s="49" t="n"/>
       <c r="G23" s="49" t="n"/>
-      <c r="H23" s="50" t="n"/>
-      <c r="I23" s="44">
-        <f>I20/H22</f>
-        <v>14.705910576547245</v>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="36">
+        <f>SUM(J5:J21)</f>
+        <v>3.7433226922120264</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>PVP CON IVA (10% hostelería)</t>
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Coste elaboración (%)</t>
         </is>
       </c>
       <c r="B24" s="49" t="n"/>
@@ -2239,15 +3040,18 @@
       <c r="F24" s="49" t="n"/>
       <c r="G24" s="49" t="n"/>
       <c r="H24" s="50" t="n"/>
-      <c r="I24" s="46">
-        <f>I23*1.10</f>
-        <v>16.17650163420197</v>
+      <c r="I24" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="38">
+        <f>J23*I24</f>
+        <v>0.37433226922120266</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
-        <is>
-          <t>Margen bruto (€)</t>
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
       <c r="B25" s="49" t="n"/>
@@ -2256,16 +3060,17 @@
       <c r="E25" s="49" t="n"/>
       <c r="F25" s="49" t="n"/>
       <c r="G25" s="49" t="n"/>
-      <c r="H25" s="50" t="n"/>
-      <c r="I25" s="38">
-        <f>I23-I20</f>
-        <v>10.588255615114015</v>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="40">
+        <f>J23+J24</f>
+        <v>4.117654961433229</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="37" t="inlineStr">
         <is>
-          <t>Margen bruto (%)</t>
+          <t>Nº de raciones</t>
         </is>
       </c>
       <c r="B26" s="49" t="n"/>
@@ -2275,32 +3080,215 @@
       <c r="F26" s="49" t="n"/>
       <c r="G26" s="49" t="n"/>
       <c r="H26" s="50" t="n"/>
-      <c r="I26" s="47">
-        <f>I25/I23</f>
+      <c r="I26" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>COSTE POR RACIÓN</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="40">
+        <f>IFERROR(J25/I26,"")</f>
+        <v>4.117654961433229</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Food Cost objetivo (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="62" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>PVP SUGERIDO (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="50" t="n"/>
+      <c r="J30" s="44">
+        <f>IFERROR(J27/I29,"")</f>
+        <v>14.705910576547245</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Tipo de IVA (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>PVP CON IVA</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="40">
+        <f>IFERROR(J30*(1+I31),"")</f>
+        <v>16.17650163420197</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Margen bruto (€)</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="44">
+        <f>IFERROR(J30-J27,"")</f>
+        <v>10.588255615114015</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>Margen bruto (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="47">
+        <f>IFERROR((J30-J27)/J30,"")</f>
         <v>0.7199999999999999</v>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>PVP actual en carta (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="63" t="n"/>
+      <c r="J36" s="38" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>FOOD COST REAL (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="49" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="64">
+        <f>IFERROR(J27/I36,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A20:H20"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G5:G21">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"?"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISNUMBER($J$37),$J$37&gt;$I$29)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
-      <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
+    <dataValidation sqref="B5:B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista (hoja «Mermas»)." type="list">
+      <formula1>Mermas!$A$5:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C21 F5:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una unidad de la lista." type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2324,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2333,12 +3321,13 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2348,22 +3337,22 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>Introduce tus ingredientes y cantidades. Las celdas verdes son editables.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="K3" s="10" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>📷 Foto del Plato</t>
         </is>
       </c>
-      <c r="L3" s="48" t="n"/>
-    </row>
-    <row r="4">
+      <c r="M3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Ingrediente</t>
@@ -2396,449 +3385,562 @@
       </c>
       <c r="G4" s="12" t="inlineStr">
         <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
           <t>Merma (%)</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Cant. Bruta</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Coste (€)</t>
         </is>
       </c>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="14" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>English muffin</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>Pan/bollería</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="54" t="n">
         <v>0.4</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="56">
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="20">
-        <f>E5/(1-G5)</f>
+      <c r="I5" s="20">
+        <f>IFERROR(IF(E5="","",E5/(1-H5)),"revisa merma")</f>
         <v>2.0</v>
       </c>
-      <c r="I5" s="21">
-        <f>H5*D5</f>
+      <c r="J5" s="21">
+        <f>IF(G5="?","revisa unidades",IFERROR(I5*D5/G5,""))</f>
         <v>0.8</v>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="23" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Huevo campero</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>Huevos</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>docena</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="54" t="n">
         <v>4.2</v>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="E6" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>ud</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H6" s="20">
-        <f>E6/(1-G6)</f>
-        <v>0.18764044943820227</v>
-      </c>
-      <c r="I6" s="21">
-        <f>H6*D6</f>
-        <v>0.7880898876404495</v>
-      </c>
-      <c r="K6" s="22" t="n"/>
-      <c r="L6" s="23" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="G6" s="56">
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>12.0</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="20">
+        <f>IFERROR(IF(E6="","",E6/(1-H6)),"revisa merma")</f>
+        <v>2.0</v>
+      </c>
+      <c r="J6" s="21">
+        <f>IF(G6="?","revisa unidades",IFERROR(I6*D6/G6,""))</f>
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Salmón ahumado</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>Pescado</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="54" t="n">
         <v>35</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="55" t="n">
         <v>0.06</v>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="56">
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="57" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="20">
-        <f>E7/(1-G7)</f>
+      <c r="I7" s="20">
+        <f>IFERROR(IF(E7="","",E7/(1-H7)),"revisa merma")</f>
         <v>0.06315789473684211</v>
       </c>
-      <c r="I7" s="21">
-        <f>H7*D7</f>
+      <c r="J7" s="21">
+        <f>IF(G7="?","revisa unidades",IFERROR(I7*D7/G7,""))</f>
         <v>2.210526315789474</v>
       </c>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="23" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
         <is>
           <t>Mantequilla (hollandaise)</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>Lácteos</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="54" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="55" t="n">
         <v>0.05</v>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="56">
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H8" s="57" t="n">
         <v>0.03</v>
       </c>
-      <c r="H8" s="20">
-        <f>E8/(1-G8)</f>
+      <c r="I8" s="20">
+        <f>IFERROR(IF(E8="","",E8/(1-H8)),"revisa merma")</f>
         <v>0.051546391752577324</v>
       </c>
-      <c r="I8" s="21">
-        <f>H8*D8</f>
+      <c r="J8" s="21">
+        <f>IF(G8="?","revisa unidades",IFERROR(I8*D8/G8,""))</f>
         <v>0.4639175257731959</v>
       </c>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>Arrastra aquí la foto
-del plato terminado</t>
-        </is>
-      </c>
-      <c r="L8" s="25" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Foto del plato terminado:
+Revisar → Desproteger hoja,
+luego Insertar → Imagen</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Limón</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>Fruta</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="54" t="n">
         <v>2.5</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="55" t="n">
         <v>0.01</v>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="56">
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="57" t="n">
         <v>0.28</v>
       </c>
-      <c r="H9" s="20">
-        <f>E9/(1-G9)</f>
+      <c r="I9" s="20">
+        <f>IFERROR(IF(E9="","",E9/(1-H9)),"revisa merma")</f>
         <v>0.01388888888888889</v>
       </c>
-      <c r="I9" s="21">
-        <f>H9*D9</f>
+      <c r="J9" s="21">
+        <f>IF(G9="?","revisa unidades",IFERROR(I9*D9/G9,""))</f>
         <v>0.034722222222222224</v>
       </c>
-      <c r="K9" s="26" t="n"/>
-      <c r="L9" s="27" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Cebollino</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>Cebollino (1 rama ≈ 1/12 manojo)</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>Especias/hierbas</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>manojo</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="54" t="n">
         <v>1.5</v>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>ud</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="n">
+      <c r="E10" s="55" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>manojo</t>
+        </is>
+      </c>
+      <c r="G10" s="56">
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="57" t="n">
         <v>0.2</v>
       </c>
-      <c r="H10" s="20">
-        <f>E10/(1-G10)</f>
-        <v>0.3125</v>
-      </c>
-      <c r="I10" s="21">
-        <f>H10*D10</f>
-        <v>0.46875</v>
-      </c>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="23" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="30">
-        <f>IF(E11="","",E11/(1-G11))</f>
-        <v/>
-      </c>
-      <c r="I11" s="31">
-        <f>IF(H11="","",H11*D11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="22" t="n"/>
-      <c r="L11" s="23" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="30">
-        <f>IF(E12="","",E12/(1-G12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>IF(H12="","",H12*D12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="22" t="n"/>
-      <c r="L12" s="23" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="28" t="n"/>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="30">
-        <f>IF(E13="","",E13/(1-G13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="31">
-        <f>IF(H13="","",H13*D13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="23" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="30">
-        <f>IF(E14="","",E14/(1-G14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="31">
-        <f>IF(H14="","",H14*D14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="32" t="n"/>
-      <c r="L14" s="33" t="n"/>
+      <c r="I10" s="20">
+        <f>IFERROR(IF(E10="","",E10/(1-H10)),"revisa merma")</f>
+        <v>0.10375</v>
+      </c>
+      <c r="J10" s="21">
+        <f>IF(G10="?","revisa unidades",IFERROR(I10*D10/G10,""))</f>
+        <v>0.15562499999999999</v>
+      </c>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="58" t="n"/>
+      <c r="C11" s="58" t="n"/>
+      <c r="D11" s="58" t="n"/>
+      <c r="E11" s="58" t="n"/>
+      <c r="F11" s="58" t="n"/>
+      <c r="G11" s="56">
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="59">
+        <f>IFERROR(VLOOKUP(B11,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="30">
+        <f>IFERROR(IF(E11="","",E11/(1-H11)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J11" s="31">
+        <f>IF(G11="?","revisa unidades",IFERROR(I11*D11/G11,""))</f>
+        <v/>
+      </c>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="58" t="n"/>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="58" t="n"/>
+      <c r="G12" s="56">
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>IFERROR(VLOOKUP(B12,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="30">
+        <f>IFERROR(IF(E12="","",E12/(1-H12)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J12" s="31">
+        <f>IF(G12="?","revisa unidades",IFERROR(I12*D12/G12,""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="C13" s="58" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="56">
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="59">
+        <f>IFERROR(VLOOKUP(B13,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="30">
+        <f>IFERROR(IF(E13="","",E13/(1-H13)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>IF(G13="?","revisa unidades",IFERROR(I13*D13/G13,""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="56">
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="59">
+        <f>IFERROR(VLOOKUP(B14,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>IFERROR(IF(E14="","",E14/(1-H14)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J14" s="31">
+        <f>IF(G14="?","revisa unidades",IFERROR(I14*D14/G14,""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="33" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="28" t="n"/>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="30">
-        <f>IF(E15="","",E15/(1-G15))</f>
-        <v/>
-      </c>
-      <c r="I15" s="31">
-        <f>IF(H15="","",H15*D15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="34" t="inlineStr">
-        <is>
-          <t>Insertar → Imagen → Desde archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="56">
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>IFERROR(VLOOKUP(B15,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="30">
+        <f>IFERROR(IF(E15="","",E15/(1-H15)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J15" s="31">
+        <f>IF(G15="?","revisa unidades",IFERROR(I15*D15/G15,""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="34" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="56">
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="59">
+        <f>IFERROR(VLOOKUP(B16,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="30">
+        <f>IFERROR(IF(E16="","",E16/(1-H16)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J16" s="31">
+        <f>IF(G16="?","revisa unidades",IFERROR(I16*D16/G16,""))</f>
+        <v/>
+      </c>
+      <c r="L16" s="34" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="56">
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="59">
+        <f>IFERROR(VLOOKUP(B17,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>IFERROR(IF(E17="","",E17/(1-H17)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J17" s="31">
+        <f>IF(G17="?","revisa unidades",IFERROR(I17*D17/G17,""))</f>
+        <v/>
+      </c>
+      <c r="L17" s="34" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="56">
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="59">
+        <f>IFERROR(VLOOKUP(B18,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="30">
+        <f>IFERROR(IF(E18="","",E18/(1-H18)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J18" s="31">
+        <f>IF(G18="?","revisa unidades",IFERROR(I18*D18/G18,""))</f>
+        <v/>
+      </c>
+      <c r="L18" s="34" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="n"/>
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="56">
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>IFERROR(VLOOKUP(B19,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="30">
+        <f>IFERROR(IF(E19="","",E19/(1-H19)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>IF(G19="?","revisa unidades",IFERROR(I19*D19/G19,""))</f>
+        <v/>
+      </c>
+      <c r="L19" s="34" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="n"/>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="56">
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>IFERROR(VLOOKUP(B20,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="30">
+        <f>IFERROR(IF(E20="","",E20/(1-H20)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J20" s="31">
+        <f>IF(G20="?","revisa unidades",IFERROR(I20*D20/G20,""))</f>
+        <v/>
+      </c>
+      <c r="L20" s="34" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>COSTE TOTAL INGREDIENTES</t>
-        </is>
-      </c>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="49" t="n"/>
-      <c r="G17" s="49" t="n"/>
-      <c r="H17" s="50" t="n"/>
-      <c r="I17" s="36">
-        <f>SUM(I5:I15)</f>
-        <v>4.766005951425342</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Coste elaboración (%)</t>
-        </is>
-      </c>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="49" t="n"/>
-      <c r="G18" s="50" t="n"/>
-      <c r="H18" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I18" s="38">
-        <f>I17*H18</f>
-        <v>0.4766005951425342</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>COSTE TOTAL DEL PLATO</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="49" t="n"/>
-      <c r="G19" s="49" t="n"/>
-      <c r="H19" s="50" t="n"/>
-      <c r="I19" s="40">
-        <f>I17+I18</f>
-        <v>5.242606546567876</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="41" t="inlineStr">
-        <is>
-          <t>Food Cost objetivo (%)</t>
-        </is>
-      </c>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="49" t="n"/>
-      <c r="D21" s="49" t="n"/>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="49" t="n"/>
-      <c r="G21" s="50" t="n"/>
-      <c r="H21" s="42" t="n">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>PVP SUGERIDO (sin IVA)</t>
         </is>
       </c>
       <c r="B22" s="49" t="n"/>
@@ -2847,16 +3949,17 @@
       <c r="E22" s="49" t="n"/>
       <c r="F22" s="49" t="n"/>
       <c r="G22" s="49" t="n"/>
-      <c r="H22" s="50" t="n"/>
-      <c r="I22" s="44">
-        <f>I19/H21</f>
-        <v>18.723594809170983</v>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="36">
+        <f>SUM(J5:J20)</f>
+        <v>4.3647910637848915</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t>PVP CON IVA (10% hostelería)</t>
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>Coste elaboración (%)</t>
         </is>
       </c>
       <c r="B23" s="49" t="n"/>
@@ -2866,15 +3969,18 @@
       <c r="F23" s="49" t="n"/>
       <c r="G23" s="49" t="n"/>
       <c r="H23" s="50" t="n"/>
-      <c r="I23" s="46">
-        <f>I22*1.10</f>
-        <v>20.595954290088084</v>
+      <c r="I23" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" s="38">
+        <f>J22*I23</f>
+        <v>0.4364791063784892</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>Margen bruto (€)</t>
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>COSTE TOTAL DEL PLATO</t>
         </is>
       </c>
       <c r="B24" s="49" t="n"/>
@@ -2883,16 +3989,17 @@
       <c r="E24" s="49" t="n"/>
       <c r="F24" s="49" t="n"/>
       <c r="G24" s="49" t="n"/>
-      <c r="H24" s="50" t="n"/>
-      <c r="I24" s="38">
-        <f>I22-I19</f>
-        <v>13.480988262603107</v>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="40">
+        <f>J22+J23</f>
+        <v>4.801270170163381</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="37" t="inlineStr">
         <is>
-          <t>Margen bruto (%)</t>
+          <t>Nº de raciones</t>
         </is>
       </c>
       <c r="B25" s="49" t="n"/>
@@ -2902,32 +4009,215 @@
       <c r="F25" s="49" t="n"/>
       <c r="G25" s="49" t="n"/>
       <c r="H25" s="50" t="n"/>
-      <c r="I25" s="47">
-        <f>I24/I22</f>
+      <c r="I25" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="38" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>COSTE POR RACIÓN</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="50" t="n"/>
+      <c r="J26" s="40">
+        <f>IFERROR(J24/I25,"")</f>
+        <v>4.801270170163381</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Food Cost objetivo (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="49" t="n"/>
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="50" t="n"/>
+      <c r="I28" s="62" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>PVP SUGERIDO (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="50" t="n"/>
+      <c r="J29" s="44">
+        <f>IFERROR(J26/I28,"")</f>
+        <v>17.147393464869214</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>Tipo de IVA (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="50" t="n"/>
+      <c r="I30" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J30" s="38" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
+        <is>
+          <t>PVP CON IVA</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="50" t="n"/>
+      <c r="J31" s="40">
+        <f>IFERROR(J29*(1+I30),"")</f>
+        <v>18.862132811356137</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>Margen bruto (€)</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="44">
+        <f>IFERROR(J29-J26,"")</f>
+        <v>12.346123294705833</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>Margen bruto (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="47">
+        <f>IFERROR((J29-J26)/J29,"")</f>
         <v>0.72</v>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>PVP actual en carta (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B35" s="49" t="n"/>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+      <c r="E35" s="49" t="n"/>
+      <c r="F35" s="49" t="n"/>
+      <c r="G35" s="49" t="n"/>
+      <c r="H35" s="50" t="n"/>
+      <c r="I35" s="63" t="n"/>
+      <c r="J35" s="38" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>FOOD COST REAL (%)</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="64">
+        <f>IFERROR(J26/I35,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="K8:L9"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A21:G21"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G5:G20">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"?"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J36">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISNUMBER($J$36),$J$36&gt;$I$28)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Categoría inválida" error="Selecciona una categoría válida" type="list">
-      <formula1>"Carne roja,Aves,Pescado,Marisco,Verdura hoja,Verdura raíz,Fruta,Lácteos,Secos/granos,Congelados,Pan/bollería,Huevos,Aceites/grasas,Especias/hierbas,Chocolate/cacao,Bebidas/licores"</formula1>
+    <dataValidation sqref="B5:B20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista (hoja «Mermas»)." type="list">
+      <formula1>Mermas!$A$5:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C20 F5:F20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una unidad de la lista." type="list">
       <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2942,4 +4232,1985 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFD700"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Carrot Cake con Frosting de Queso — tanda de 12 raciones (molde de 20 cm, dos capas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>Escandallo por TANDA. El «Nº de raciones» reparte el coste entre las porciones que salen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>📷 Foto del Plato</t>
+        </is>
+      </c>
+      <c r="M3" s="48" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Ingrediente</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Ud. Compra</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Precio/Ud (€)</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Cantidad</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Ud. Uso</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>Merma (%)</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>Cant. Bruta</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>Coste (€)</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="14" t="n"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>Zanahoria</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Verdura raíz</t>
+        </is>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D5" s="54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E5" s="55" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G5" s="56">
+        <f>IF(C5&amp;F5="","",IFERROR(VLOOKUP(C5&amp;"→"&amp;F5,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I5" s="20">
+        <f>IFERROR(IF(E5="","",E5/(1-H5)),"revisa merma")</f>
+        <v>0.5625</v>
+      </c>
+      <c r="J5" s="21">
+        <f>IF(G5="?","revisa unidades",IFERROR(I5*D5/G5,""))</f>
+        <v>0.7875</v>
+      </c>
+      <c r="L5" s="22" t="n"/>
+      <c r="M5" s="23" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>Harina floja</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>Secos/granos</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D6" s="54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" s="55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G6" s="56">
+        <f>IF(C6&amp;F6="","",IFERROR(VLOOKUP(C6&amp;"→"&amp;F6,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H6" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I6" s="20">
+        <f>IFERROR(IF(E6="","",E6/(1-H6)),"revisa merma")</f>
+        <v>0.30612244897959184</v>
+      </c>
+      <c r="J6" s="21">
+        <f>IF(G6="?","revisa unidades",IFERROR(I6*D6/G6,""))</f>
+        <v>0.3673469387755102</v>
+      </c>
+      <c r="L6" s="22" t="n"/>
+      <c r="M6" s="23" t="n"/>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>Azúcar moreno</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t>Secos/granos</t>
+        </is>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D7" s="54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G7" s="56">
+        <f>IF(C7&amp;F7="","",IFERROR(VLOOKUP(C7&amp;"→"&amp;F7,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H7" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I7" s="20">
+        <f>IFERROR(IF(E7="","",E7/(1-H7)),"revisa merma")</f>
+        <v>0.28571428571428575</v>
+      </c>
+      <c r="J7" s="21">
+        <f>IF(G7="?","revisa unidades",IFERROR(I7*D7/G7,""))</f>
+        <v>0.6285714285714287</v>
+      </c>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="23" t="n"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>Huevo campero</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>docena</t>
+        </is>
+      </c>
+      <c r="D8" s="54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E8" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>ud</t>
+        </is>
+      </c>
+      <c r="G8" s="56">
+        <f>IF(C8&amp;F8="","",IFERROR(VLOOKUP(C8&amp;"→"&amp;F8,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>12.0</v>
+      </c>
+      <c r="H8" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="20">
+        <f>IFERROR(IF(E8="","",E8/(1-H8)),"revisa merma")</f>
+        <v>6.0</v>
+      </c>
+      <c r="J8" s="21">
+        <f>IF(G8="?","revisa unidades",IFERROR(I8*D8/G8,""))</f>
+        <v>2.1</v>
+      </c>
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <t>Foto del plato terminado:
+Revisar → Desproteger hoja,
+luego Insertar → Imagen</t>
+        </is>
+      </c>
+      <c r="M8" s="25" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>Aceite de girasol</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>Aceites/grasas</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D9" s="54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E9" s="55" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G9" s="56">
+        <f>IF(C9&amp;F9="","",IFERROR(VLOOKUP(C9&amp;"→"&amp;F9,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="20">
+        <f>IFERROR(IF(E9="","",E9/(1-H9)),"revisa merma")</f>
+        <v>0.24</v>
+      </c>
+      <c r="J9" s="21">
+        <f>IF(G9="?","revisa unidades",IFERROR(I9*D9/G9,""))</f>
+        <v>0.576</v>
+      </c>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="27" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>Nueces peladas</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Secos/granos</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D10" s="54" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="55" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G10" s="56">
+        <f>IF(C10&amp;F10="","",IFERROR(VLOOKUP(C10&amp;"→"&amp;F10,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H10" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="20">
+        <f>IFERROR(IF(E10="","",E10/(1-H10)),"revisa merma")</f>
+        <v>0.12631578947368421</v>
+      </c>
+      <c r="J10" s="21">
+        <f>IF(G10="?","revisa unidades",IFERROR(I10*D10/G10,""))</f>
+        <v>2.0210526315789474</v>
+      </c>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="52" t="inlineStr">
+        <is>
+          <t>Canela molida</t>
+        </is>
+      </c>
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Especias/hierbas</t>
+        </is>
+      </c>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D11" s="54" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" s="55" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F11" s="53" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G11" s="56">
+        <f>IF(C11&amp;F11="","",IFERROR(VLOOKUP(C11&amp;"→"&amp;F11,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H11" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I11" s="20">
+        <f>IFERROR(IF(E11="","",E11/(1-H11)),"revisa merma")</f>
+        <v>0.00816326530612245</v>
+      </c>
+      <c r="J11" s="21">
+        <f>IF(G11="?","revisa unidades",IFERROR(I11*D11/G11,""))</f>
+        <v>0.2612244897959184</v>
+      </c>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="23" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>Queso crema (frosting)</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D12" s="58" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E12" s="58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F12" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G12" s="56">
+        <f>IF(C12&amp;F12="","",IFERROR(VLOOKUP(C12&amp;"→"&amp;F12,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H12" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="30">
+        <f>IFERROR(IF(E12="","",E12/(1-H12)),"revisa merma")</f>
+        <v>0.4639175257731959</v>
+      </c>
+      <c r="J12" s="31">
+        <f>IF(G12="?","revisa unidades",IFERROR(I12*D12/G12,""))</f>
+        <v>3.6649484536082477</v>
+      </c>
+      <c r="L12" s="22" t="n"/>
+      <c r="M12" s="23" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>Azúcar glas (frosting)</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Secos/granos</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G13" s="56">
+        <f>IF(C13&amp;F13="","",IFERROR(VLOOKUP(C13&amp;"→"&amp;F13,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I13" s="30">
+        <f>IFERROR(IF(E13="","",E13/(1-H13)),"revisa merma")</f>
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="J13" s="31">
+        <f>IF(G13="?","revisa unidades",IFERROR(I13*D13/G13,""))</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="L13" s="22" t="n"/>
+      <c r="M13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>Mantequilla (frosting)</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D14" s="58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E14" s="58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F14" s="58" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G14" s="56">
+        <f>IF(C14&amp;F14="","",IFERROR(VLOOKUP(C14&amp;"→"&amp;F14,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v>1.0</v>
+      </c>
+      <c r="H14" s="59" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I14" s="30">
+        <f>IFERROR(IF(E14="","",E14/(1-H14)),"revisa merma")</f>
+        <v>0.12371134020618557</v>
+      </c>
+      <c r="J14" s="31">
+        <f>IF(G14="?","revisa unidades",IFERROR(I14*D14/G14,""))</f>
+        <v>1.2989690721649485</v>
+      </c>
+      <c r="L14" s="32" t="n"/>
+      <c r="M14" s="33" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="56">
+        <f>IF(C15&amp;F15="","",IFERROR(VLOOKUP(C15&amp;"→"&amp;F15,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="59">
+        <f>IFERROR(VLOOKUP(B15,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="30">
+        <f>IFERROR(IF(E15="","",E15/(1-H15)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J15" s="31">
+        <f>IF(G15="?","revisa unidades",IFERROR(I15*D15/G15,""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="34" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="56">
+        <f>IF(C16&amp;F16="","",IFERROR(VLOOKUP(C16&amp;"→"&amp;F16,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="59">
+        <f>IFERROR(VLOOKUP(B16,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="30">
+        <f>IFERROR(IF(E16="","",E16/(1-H16)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J16" s="31">
+        <f>IF(G16="?","revisa unidades",IFERROR(I16*D16/G16,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="58" t="n"/>
+      <c r="C17" s="58" t="n"/>
+      <c r="D17" s="58" t="n"/>
+      <c r="E17" s="58" t="n"/>
+      <c r="F17" s="58" t="n"/>
+      <c r="G17" s="56">
+        <f>IF(C17&amp;F17="","",IFERROR(VLOOKUP(C17&amp;"→"&amp;F17,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="59">
+        <f>IFERROR(VLOOKUP(B17,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>IFERROR(IF(E17="","",E17/(1-H17)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J17" s="31">
+        <f>IF(G17="?","revisa unidades",IFERROR(I17*D17/G17,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="56">
+        <f>IF(C18&amp;F18="","",IFERROR(VLOOKUP(C18&amp;"→"&amp;F18,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="59">
+        <f>IFERROR(VLOOKUP(B18,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="30">
+        <f>IFERROR(IF(E18="","",E18/(1-H18)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J18" s="31">
+        <f>IF(G18="?","revisa unidades",IFERROR(I18*D18/G18,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="n"/>
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="56">
+        <f>IF(C19&amp;F19="","",IFERROR(VLOOKUP(C19&amp;"→"&amp;F19,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="59">
+        <f>IFERROR(VLOOKUP(B19,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="30">
+        <f>IFERROR(IF(E19="","",E19/(1-H19)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J19" s="31">
+        <f>IF(G19="?","revisa unidades",IFERROR(I19*D19/G19,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="n"/>
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="56">
+        <f>IF(C20&amp;F20="","",IFERROR(VLOOKUP(C20&amp;"→"&amp;F20,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="59">
+        <f>IFERROR(VLOOKUP(B20,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="30">
+        <f>IFERROR(IF(E20="","",E20/(1-H20)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J20" s="31">
+        <f>IF(G20="?","revisa unidades",IFERROR(I20*D20/G20,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="n"/>
+      <c r="B21" s="58" t="n"/>
+      <c r="C21" s="58" t="n"/>
+      <c r="D21" s="58" t="n"/>
+      <c r="E21" s="58" t="n"/>
+      <c r="F21" s="58" t="n"/>
+      <c r="G21" s="56">
+        <f>IF(C21&amp;F21="","",IFERROR(VLOOKUP(C21&amp;"→"&amp;F21,Conversiones!$A$5:$B$37,2,FALSE),"?"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="59">
+        <f>IFERROR(VLOOKUP(B21,Mermas!$A$5:$C$25,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="30">
+        <f>IFERROR(IF(E21="","",E21/(1-H21)),"revisa merma")</f>
+        <v/>
+      </c>
+      <c r="J21" s="31">
+        <f>IF(G21="?","revisa unidades",IFERROR(I21*D21/G21,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>COSTE TOTAL INGREDIENTES</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="49" t="n"/>
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="36">
+        <f>SUM(J5:J21)</f>
+        <v>12.277041585923573</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>Coste elaboración (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="49" t="n"/>
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="38">
+        <f>J23*I24</f>
+        <v>1.2277041585923574</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>COSTE TOTAL DEL PLATO</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="49" t="n"/>
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="40">
+        <f>J23+J24</f>
+        <v>13.504745744515931</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>Nº de raciones</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="49" t="n"/>
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" s="38" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>COSTE POR RACIÓN</t>
+        </is>
+      </c>
+      <c r="B27" s="49" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="49" t="n"/>
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="40">
+        <f>IFERROR(J25/I26,"")</f>
+        <v>1.125395478709661</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Food Cost objetivo (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="49" t="n"/>
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="62" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>PVP SUGERIDO (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="49" t="n"/>
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="50" t="n"/>
+      <c r="J30" s="44">
+        <f>IFERROR(J27/I29,"")</f>
+        <v>4.501581914838644</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>Tipo de IVA (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="49" t="n"/>
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J31" s="38" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>PVP CON IVA</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="49" t="n"/>
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="40">
+        <f>IFERROR(J30*(1+I31),"")</f>
+        <v>4.951740106322508</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>Margen bruto (€)</t>
+        </is>
+      </c>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="49" t="n"/>
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="44">
+        <f>IFERROR(J30-J27,"")</f>
+        <v>3.376186436128983</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>Margen bruto (%)</t>
+        </is>
+      </c>
+      <c r="B34" s="49" t="n"/>
+      <c r="C34" s="49" t="n"/>
+      <c r="D34" s="49" t="n"/>
+      <c r="E34" s="49" t="n"/>
+      <c r="F34" s="49" t="n"/>
+      <c r="G34" s="49" t="n"/>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="47">
+        <f>IFERROR((J30-J27)/J30,"")</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>PVP actual en carta (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B36" s="49" t="n"/>
+      <c r="C36" s="49" t="n"/>
+      <c r="D36" s="49" t="n"/>
+      <c r="E36" s="49" t="n"/>
+      <c r="F36" s="49" t="n"/>
+      <c r="G36" s="49" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="63" t="n"/>
+      <c r="J36" s="38" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>FOOD COST REAL (%)</t>
+        </is>
+      </c>
+      <c r="B37" s="49" t="n"/>
+      <c r="C37" s="49" t="n"/>
+      <c r="D37" s="49" t="n"/>
+      <c r="E37" s="49" t="n"/>
+      <c r="F37" s="49" t="n"/>
+      <c r="G37" s="49" t="n"/>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="64">
+        <f>IFERROR(J27/I36,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G21">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"?"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(ISNUMBER($J$37),$J$37&gt;$I$29)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B5:B21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una categoría de la lista (hoja «Mermas»)." type="list">
+      <formula1>Mermas!$A$5:$A$25</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C21 F5:F21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige una unidad de la lista." type="list">
+      <formula1>"kg,g,L,ml,cl,ud,docena,manojo,sobre,lata,botella"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>Tabla de conversión Ud. Compra → Ud. Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>La usa la columna «Factor» de cada escandallo. Puedes añadir parejas al final: la clave se escribe «compra→uso».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Conversión (compra→uso)</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>Qué significa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kg→kg</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kg→g</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1 kg = 1.000 g</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>g→g</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>g→kg</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1 g = 0,001 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L→L</t>
+        </is>
+      </c>
+      <c r="B9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>L→ml</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1 L = 1.000 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>L→cl</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1 L = 100 cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ml→ml</t>
+        </is>
+      </c>
+      <c r="B12" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ml→L</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1 ml = 0,001 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ml→cl</t>
+        </is>
+      </c>
+      <c r="B14" s="67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1 ml = 0,1 cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cl→cl</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cl→ml</t>
+        </is>
+      </c>
+      <c r="B16" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1 cl = 10 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cl→L</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1 cl = 0,01 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ud→ud</t>
+        </is>
+      </c>
+      <c r="B18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>docena→ud</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1 docena = 12 ud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>docena→docena</t>
+        </is>
+      </c>
+      <c r="B20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ud→docena</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1 ud = 1/12 docena</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>manojo→manojo</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>manojo→ud</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>el manojo se compra y se usa como unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sobre→sobre</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sobre→ud</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>el sobre se compra y se usa como unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>lata→lata</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>lata→ud</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>la lata se compra y se usa como unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>botella→botella</t>
+        </is>
+      </c>
+      <c r="B28" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>misma unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>botella→ud</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>la botella se compra y se usa como unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>botella→cl</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="n">
+        <v>70</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>botella de 70 cl (destilados). Vino: cambia el 70 por 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>botella→ml</t>
+        </is>
+      </c>
+      <c r="B31" s="67" t="n">
+        <v>700</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>botella de 70 cl = 700 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>botella→L</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>botella de 70 cl = 0,7 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>lata→cl</t>
+        </is>
+      </c>
+      <c r="B33" s="67" t="n">
+        <v>33</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>lata de 33 cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>lata→ml</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="n">
+        <v>330</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lata de 33 cl = 330 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>lata→L</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lata de 33 cl = 0,33 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>manojo→g</t>
+        </is>
+      </c>
+      <c r="B36" s="67" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>manojo de hierbas ≈ 30 g</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sobre→g</t>
+        </is>
+      </c>
+      <c r="B37" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sobre ≈ 10 g</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="inlineStr">
+        <is>
+          <t>Mermas de referencia por categoría</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>La «típica» es la que se precarga en las filas vacías del escandallo al elegir categoría. Ajústala a tu proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>Merma típica</t>
+        </is>
+      </c>
+      <c r="C4" s="66" t="inlineStr">
+        <is>
+          <t>Mínima</t>
+        </is>
+      </c>
+      <c r="D4" s="66" t="inlineStr">
+        <is>
+          <t>Máxima</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Carne roja</t>
+        </is>
+      </c>
+      <c r="B5" s="68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" s="68" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B6" s="68" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="68" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pescado</t>
+        </is>
+      </c>
+      <c r="B7" s="68" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C7" s="68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="68" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Marisco</t>
+        </is>
+      </c>
+      <c r="B8" s="68" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C8" s="68" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D8" s="68" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Verdura hoja</t>
+        </is>
+      </c>
+      <c r="B9" s="68" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="68" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Verdura raíz</t>
+        </is>
+      </c>
+      <c r="B10" s="68" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C10" s="68" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D10" s="68" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Verdura fruto</t>
+        </is>
+      </c>
+      <c r="B11" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="68" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D11" s="68" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fruta</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C12" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="68" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lácteos</t>
+        </is>
+      </c>
+      <c r="B13" s="68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D13" s="68" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Secos/granos</t>
+        </is>
+      </c>
+      <c r="B14" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C14" s="68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D14" s="68" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Congelados</t>
+        </is>
+      </c>
+      <c r="B15" s="68" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C15" s="68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D15" s="68" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pan/bollería</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C16" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D16" s="68" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Huevos</t>
+        </is>
+      </c>
+      <c r="B17" s="68" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C17" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D17" s="68" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Aceites/grasas</t>
+        </is>
+      </c>
+      <c r="B18" s="68" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C18" s="68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D18" s="68" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Especias/hierbas</t>
+        </is>
+      </c>
+      <c r="B19" s="68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C19" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="68" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chocolate/cacao</t>
+        </is>
+      </c>
+      <c r="B20" s="68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C20" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D20" s="68" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bebidas/licores</t>
+        </is>
+      </c>
+      <c r="B21" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C21" s="68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D21" s="68" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Setas/hongos</t>
+        </is>
+      </c>
+      <c r="B22" s="68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C22" s="68" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D22" s="68" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Conservas/encurtidos</t>
+        </is>
+      </c>
+      <c r="B23" s="68" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C23" s="68" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D23" s="68" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Salsas/condimentos</t>
+        </is>
+      </c>
+      <c r="B24" s="68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C24" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="68" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pasta/arroz</t>
+        </is>
+      </c>
+      <c r="B25" s="68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C25" s="68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D25" s="68" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>